--- a/aircraft/reports/aircraft-type-trends-yearly.xlsx
+++ b/aircraft/reports/aircraft-type-trends-yearly.xlsx
@@ -841,7 +841,7 @@
         <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D8" t="n">
         <v>91</v>
@@ -865,10 +865,10 @@
         <v>97</v>
       </c>
       <c r="K8" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L8" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M8" t="n">
         <v>169</v>
@@ -877,7 +877,7 @@
         <v>32</v>
       </c>
       <c r="O8" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P8" t="n">
         <v>32</v>

--- a/aircraft/reports/aircraft-type-trends-yearly.xlsx
+++ b/aircraft/reports/aircraft-type-trends-yearly.xlsx
@@ -850,7 +850,7 @@
         <v>83</v>
       </c>
       <c r="F8" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G8" t="n">
         <v>278</v>

--- a/aircraft/reports/aircraft-type-trends-yearly.xlsx
+++ b/aircraft/reports/aircraft-type-trends-yearly.xlsx
@@ -841,7 +841,7 @@
         <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D8" t="n">
         <v>91</v>
@@ -850,7 +850,7 @@
         <v>83</v>
       </c>
       <c r="F8" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G8" t="n">
         <v>278</v>
@@ -865,10 +865,10 @@
         <v>97</v>
       </c>
       <c r="K8" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="L8" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M8" t="n">
         <v>169</v>
@@ -877,7 +877,7 @@
         <v>32</v>
       </c>
       <c r="O8" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P8" t="n">
         <v>32</v>

--- a/aircraft/reports/aircraft-type-trends-yearly.xlsx
+++ b/aircraft/reports/aircraft-type-trends-yearly.xlsx
@@ -841,7 +841,7 @@
         <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D8" t="n">
         <v>91</v>
@@ -850,7 +850,7 @@
         <v>83</v>
       </c>
       <c r="F8" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G8" t="n">
         <v>278</v>
@@ -865,19 +865,19 @@
         <v>97</v>
       </c>
       <c r="K8" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L8" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M8" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N8" t="n">
         <v>32</v>
       </c>
       <c r="O8" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P8" t="n">
         <v>32</v>

--- a/aircraft/reports/aircraft-type-trends-yearly.xlsx
+++ b/aircraft/reports/aircraft-type-trends-yearly.xlsx
@@ -841,37 +841,37 @@
         <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D8" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E8" t="n">
         <v>83</v>
       </c>
       <c r="F8" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G8" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H8" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="I8" t="n">
         <v>26</v>
       </c>
       <c r="J8" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K8" t="n">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="L8" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M8" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="N8" t="n">
         <v>32</v>
@@ -883,7 +883,7 @@
         <v>32</v>
       </c>
       <c r="Q8" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/aircraft/reports/aircraft-type-trends-yearly.xlsx
+++ b/aircraft/reports/aircraft-type-trends-yearly.xlsx
@@ -841,10 +841,10 @@
         <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="D8" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E8" t="n">
         <v>83</v>
@@ -856,16 +856,16 @@
         <v>279</v>
       </c>
       <c r="H8" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I8" t="n">
         <v>26</v>
       </c>
       <c r="J8" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K8" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="L8" t="n">
         <v>93</v>
@@ -883,7 +883,7 @@
         <v>32</v>
       </c>
       <c r="Q8" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/aircraft/reports/aircraft-type-trends-yearly.xlsx
+++ b/aircraft/reports/aircraft-type-trends-yearly.xlsx
@@ -841,22 +841,22 @@
         <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D8" t="n">
         <v>93</v>
       </c>
       <c r="E8" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F8" t="n">
         <v>64</v>
       </c>
       <c r="G8" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H8" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I8" t="n">
         <v>26</v>
@@ -865,25 +865,25 @@
         <v>99</v>
       </c>
       <c r="K8" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L8" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M8" t="n">
         <v>172</v>
       </c>
       <c r="N8" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O8" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P8" t="n">
         <v>32</v>
       </c>
       <c r="Q8" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
